--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery Charger Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97F40DE-E9D0-48C9-B9CF-794E54FC0406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DF3313-3E1C-4ED8-9B3C-2A9C410F5E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
-    <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
-    <sheet name="12V analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="24V analysis V2" sheetId="1" r:id="rId1"/>
+    <sheet name="12V analysis V2" sheetId="2" r:id="rId2"/>
+    <sheet name="24V analysis V1" sheetId="4" r:id="rId3"/>
+    <sheet name="12V analysis V1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="65">
   <si>
     <t>C-rate</t>
   </si>
@@ -2077,7 +2079,7 @@
         <v>64</v>
       </c>
       <c r="N5" s="7">
-        <f>'24V analysis'!N6</f>
+        <f>'24V analysis V2'!N6</f>
         <v>6.5886173588108662E-5</v>
       </c>
       <c r="O5" s="8" t="s">
@@ -2336,6 +2338,1111 @@
       <c r="F21" s="13">
         <f>F18*F20</f>
         <v>1.5427784316797402</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="13">
+        <f>F19*F20</f>
+        <v>21.6</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="13">
+        <v>500</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="E24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E26" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="13">
+        <f>F24*F20</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E27" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="14">
+        <f>F25*F17</f>
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="E13:G13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A603C2-9CB9-4EDD-96B4-465A647A4A00}">
+  <dimension ref="A1:R28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.109375" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="24"/>
+      <c r="E1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="G1" s="20"/>
+      <c r="I1" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="19"/>
+      <c r="K1" s="20"/>
+      <c r="M1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="13">
+        <f>F4/SQRT(2)</f>
+        <v>24.024478110041532</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="13">
+        <f>F17/F19</f>
+        <v>32.444444444444443</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" s="17">
+        <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
+        <v>6.5167593819901747E-6</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="13">
+        <v>110</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="13">
+        <f>((3/PI())*F5)</f>
+        <v>148.55219216592252</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3">
+        <f>((F19*F14)*(1-F19))/(F26*F23*10^3)</f>
+        <v>8.1111111111111105E-7</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <f>B2*B3</f>
+        <v>24</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="13">
+        <f>((PI()/3)*J2)</f>
+        <v>33.975742772156281</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="13">
+        <f>B18</f>
+        <v>480</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4">
+        <f>(((1-F18)*B20)/(2*F23*10^3))</f>
+        <v>7.2113931974347563E-7</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2.5</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="13">
+        <f>SQRT(2)*F3</f>
+        <v>155.56349186104046</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="13">
+        <f>B19</f>
+        <v>700.8</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5">
+        <f>((1-('12V analysis V1'!F18))/(8*N2*F25*(F23*10^3)^2))</f>
+        <v>7.1560382789616669E-6</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R5" s="11"/>
+    </row>
+    <row r="6" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3.65</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="13">
+        <f>SQRT(2/3)*J6</f>
+        <v>2.6382536207043161</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="13">
+        <f>F21</f>
+        <v>3.231187591387902</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" s="7">
+        <f>N2</f>
+        <v>6.5167593819901747E-6</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="13">
+        <f>SQRT(2/3)*J7</f>
+        <v>17.636326148038883</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="14">
+        <f>F22</f>
+        <v>21.6</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="13">
+        <f>SQRT(3)*F6*F3</f>
+        <v>502.65482457436673</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="14">
+        <f>SQRT(3)*F2*F7</f>
+        <v>733.8760438785755</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M10" s="13"/>
+    </row>
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="E13" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="13">
+        <f>J2</f>
+        <v>32.444444444444443</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="E15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="13">
+        <f>J3</f>
+        <v>148.55219216592252</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <f>B5*B15</f>
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="13">
+        <f>B16</f>
+        <v>20</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <f>B6*B15</f>
+        <v>29.2</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="13">
+        <f>B17</f>
+        <v>29.2</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <f>B16*B4</f>
+        <v>480</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="13">
+        <f>F16/J3</f>
+        <v>0.13463281630782925</v>
+      </c>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <f>B17*B4</f>
+        <v>700.8</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="13">
+        <f>B16/B4</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="13">
+        <v>24</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="14">
+        <f>B17/B4</f>
+        <v>1.2166666666666666</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="13">
+        <f>F18*F20</f>
+        <v>3.231187591387902</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="13">
+        <f>F19*F20</f>
+        <v>21.6</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="13">
+        <v>500</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="E24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E26" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="13">
+        <f>F24*F20</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="13">
+        <f>F25*F17</f>
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" s="7">
+        <f>SQRT(((F20^2)+(3.6^2)))</f>
+        <v>24.268498099388022</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0420058C-2B98-43A8-B8E2-0DAD44F0257E}">
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="24"/>
+      <c r="E1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="G1" s="20"/>
+      <c r="I1" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="19"/>
+      <c r="K1" s="20"/>
+      <c r="M1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="19"/>
+      <c r="O1" s="20"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="13">
+        <f>F4/SQRT(2)</f>
+        <v>12.012239055020766</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="13">
+        <f>F17/F19</f>
+        <v>16.222222222222221</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2">
+        <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
+        <v>3.6569676232753216E-6</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="13">
+        <v>110</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="13">
+        <f>((3/PI())*F5)</f>
+        <v>148.55219216592252</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3">
+        <f>((F19*F14)*(1-F19))/(F26*F23*10^3)</f>
+        <v>4.0555555555555553E-7</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <f>B2*B3</f>
+        <v>24</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="13">
+        <f>((PI()/3)*J2)</f>
+        <v>16.98787138607814</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="13">
+        <f>B18</f>
+        <v>240</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4">
+        <f>(((1-F18)*B20)/(2*F23*10^3))</f>
+        <v>3.8861816326920227E-7</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2.5</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="13">
+        <f>SQRT(2)*F3</f>
+        <v>155.56349186104046</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="13">
+        <f>B19</f>
+        <v>350.4</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="7">
+        <f>'24V analysis V1'!N6</f>
+        <v>6.5167593819901747E-6</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3.65</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="13">
+        <f>SQRT(2/3)*J6</f>
+        <v>1.3191268103521581</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="13">
+        <f>F21</f>
+        <v>1.615593795693951</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="13">
+        <f>SQRT(2/3)*J7</f>
+        <v>17.636326148038883</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="14">
+        <f>F22</f>
+        <v>21.6</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="13">
+        <f>SQRT(3)*F6*F3</f>
+        <v>251.32741228718336</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="14">
+        <f>SQRT(3)*F2*F7</f>
+        <v>366.93802193928775</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="E13" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="13">
+        <f>J2</f>
+        <v>16.222222222222221</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="E15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="13">
+        <f>J3</f>
+        <v>148.55219216592252</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <f>B5*B15</f>
+        <v>10</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="13">
+        <f>B16</f>
+        <v>10</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <f>B6*B15</f>
+        <v>14.6</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="13">
+        <f>B17</f>
+        <v>14.6</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <f>B16*B4</f>
+        <v>240</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="13">
+        <f>F16/J3</f>
+        <v>6.7316408153914625E-2</v>
+      </c>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <f>B17*B4</f>
+        <v>350.4</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="13">
+        <f>B16/B4</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="13">
+        <v>24</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="14">
+        <f>B17/B4</f>
+        <v>0.60833333333333328</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="13">
+        <f>F18*F20</f>
+        <v>1.615593795693951</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>30</v>
@@ -2424,23 +3531,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2629,10 +3719,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2655,20 +3773,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DF3313-3E1C-4ED8-9B3C-2A9C410F5E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1EA3CA-0187-40E0-B44F-10DD8DCC7EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
-    <sheet name="24V analysis V2" sheetId="1" r:id="rId1"/>
-    <sheet name="12V analysis V2" sheetId="2" r:id="rId2"/>
-    <sheet name="24V analysis V1" sheetId="4" r:id="rId3"/>
-    <sheet name="12V analysis V1" sheetId="5" r:id="rId4"/>
+    <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
+    <sheet name="12V analysis" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="65">
   <si>
     <t>C-rate</t>
   </si>
@@ -2079,7 +2077,7 @@
         <v>64</v>
       </c>
       <c r="N5" s="7">
-        <f>'24V analysis V2'!N6</f>
+        <f>'24V analysis'!N6</f>
         <v>6.5886173588108662E-5</v>
       </c>
       <c r="O5" s="8" t="s">
@@ -2338,1111 +2336,6 @@
       <c r="F21" s="13">
         <f>F18*F20</f>
         <v>1.5427784316797402</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="13">
-        <f>F19*F20</f>
-        <v>21.6</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="13">
-        <v>500</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="E24" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E26" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="13">
-        <f>F24*F20</f>
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="14">
-        <f>F25*F17</f>
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="E13:G13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A603C2-9CB9-4EDD-96B4-465A647A4A00}">
-  <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" customWidth="1"/>
-    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="E1" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20"/>
-      <c r="I1" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20"/>
-      <c r="M1" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20"/>
-    </row>
-    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="13">
-        <f>F4/SQRT(2)</f>
-        <v>24.024478110041532</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="13">
-        <f>F17/F19</f>
-        <v>32.444444444444443</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2" s="17">
-        <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
-        <v>6.5167593819901747E-6</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="13">
-        <v>110</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="13">
-        <f>((3/PI())*F5)</f>
-        <v>148.55219216592252</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3">
-        <f>((F19*F14)*(1-F19))/(F26*F23*10^3)</f>
-        <v>8.1111111111111105E-7</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <f>B2*B3</f>
-        <v>24</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="13">
-        <f>((PI()/3)*J2)</f>
-        <v>33.975742772156281</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="13">
-        <f>B18</f>
-        <v>480</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4">
-        <f>(((1-F18)*B20)/(2*F23*10^3))</f>
-        <v>7.2113931974347563E-7</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2.5</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="13">
-        <f>SQRT(2)*F3</f>
-        <v>155.56349186104046</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="13">
-        <f>B19</f>
-        <v>700.8</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5">
-        <f>((1-('12V analysis V1'!F18))/(8*N2*F25*(F23*10^3)^2))</f>
-        <v>7.1560382789616669E-6</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="R5" s="11"/>
-    </row>
-    <row r="6" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7">
-        <v>3.65</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="13">
-        <f>SQRT(2/3)*J6</f>
-        <v>2.6382536207043161</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="13">
-        <f>F21</f>
-        <v>3.231187591387902</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" s="7">
-        <f>N2</f>
-        <v>6.5167593819901747E-6</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="13">
-        <f>SQRT(2/3)*J7</f>
-        <v>17.636326148038883</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="14">
-        <f>F22</f>
-        <v>21.6</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="13">
-        <f>SQRT(3)*F6*F3</f>
-        <v>502.65482457436673</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="14">
-        <f>SQRT(3)*F2*F7</f>
-        <v>733.8760438785755</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="M10" s="13"/>
-    </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="E13" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="13">
-        <f>J2</f>
-        <v>32.444444444444443</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="E15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="13">
-        <f>J3</f>
-        <v>148.55219216592252</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16">
-        <f>B5*B15</f>
-        <v>20</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="13">
-        <f>B16</f>
-        <v>20</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17">
-        <f>B6*B15</f>
-        <v>29.2</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="13">
-        <f>B17</f>
-        <v>29.2</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18">
-        <f>B16*B4</f>
-        <v>480</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="13">
-        <f>F16/J3</f>
-        <v>0.13463281630782925</v>
-      </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19">
-        <f>B17*B4</f>
-        <v>700.8</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="13">
-        <f>B16/B4</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="13">
-        <v>24</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="14">
-        <f>B17/B4</f>
-        <v>1.2166666666666666</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="13">
-        <f>F18*F20</f>
-        <v>3.231187591387902</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="13">
-        <f>F19*F20</f>
-        <v>21.6</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="13">
-        <v>500</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="E24" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E25" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="13">
-        <f>F24*F20</f>
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="13">
-        <f>F25*F17</f>
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E28" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28" s="7">
-        <f>SQRT(((F20^2)+(3.6^2)))</f>
-        <v>24.268498099388022</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0420058C-2B98-43A8-B8E2-0DAD44F0257E}">
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="E1" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20"/>
-      <c r="I1" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20"/>
-      <c r="M1" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="13">
-        <f>F4/SQRT(2)</f>
-        <v>12.012239055020766</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="13">
-        <f>F17/F19</f>
-        <v>16.222222222222221</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2">
-        <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
-        <v>3.6569676232753216E-6</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="13">
-        <v>110</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="13">
-        <f>((3/PI())*F5)</f>
-        <v>148.55219216592252</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3">
-        <f>((F19*F14)*(1-F19))/(F26*F23*10^3)</f>
-        <v>4.0555555555555553E-7</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <f>B2*B3</f>
-        <v>24</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="13">
-        <f>((PI()/3)*J2)</f>
-        <v>16.98787138607814</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="13">
-        <f>B18</f>
-        <v>240</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4">
-        <f>(((1-F18)*B20)/(2*F23*10^3))</f>
-        <v>3.8861816326920227E-7</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>2.5</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="13">
-        <f>SQRT(2)*F3</f>
-        <v>155.56349186104046</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="13">
-        <f>B19</f>
-        <v>350.4</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="7">
-        <f>'24V analysis V1'!N6</f>
-        <v>6.5167593819901747E-6</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7">
-        <v>3.65</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="13">
-        <f>SQRT(2/3)*J6</f>
-        <v>1.3191268103521581</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="13">
-        <f>F21</f>
-        <v>1.615593795693951</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="13">
-        <f>SQRT(2/3)*J7</f>
-        <v>17.636326148038883</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="14">
-        <f>F22</f>
-        <v>21.6</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="13">
-        <f>SQRT(3)*F6*F3</f>
-        <v>251.32741228718336</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="14">
-        <f>SQRT(3)*F2*F7</f>
-        <v>366.93802193928775</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="12"/>
-    </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="E13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2">
-        <v>12</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="13">
-        <f>J2</f>
-        <v>16.222222222222221</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="E15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="13">
-        <f>J3</f>
-        <v>148.55219216592252</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16">
-        <f>B5*B15</f>
-        <v>10</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="13">
-        <f>B16</f>
-        <v>10</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17">
-        <f>B6*B15</f>
-        <v>14.6</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="13">
-        <f>B17</f>
-        <v>14.6</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18">
-        <f>B16*B4</f>
-        <v>240</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="13">
-        <f>F16/J3</f>
-        <v>6.7316408153914625E-2</v>
-      </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19">
-        <f>B17*B4</f>
-        <v>350.4</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="13">
-        <f>B16/B4</f>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="13">
-        <v>24</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="14">
-        <f>B17/B4</f>
-        <v>0.60833333333333328</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="13">
-        <f>F18*F20</f>
-        <v>1.615593795693951</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>30</v>
@@ -3531,6 +2424,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -3719,38 +2629,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3773,9 +2655,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1EA3CA-0187-40E0-B44F-10DD8DCC7EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6437BE-D93E-4E78-BBBA-A190F34A7002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="65">
   <si>
     <t>C-rate</t>
   </si>
@@ -547,38 +547,6 @@
   </si>
   <si>
     <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>min</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CCM,th</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>V</t>
     </r>
     <r>
@@ -713,22 +681,6 @@
   </si>
   <si>
     <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ccm,th</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>C</t>
     </r>
     <r>
@@ -766,7 +718,16 @@
     </r>
   </si>
   <si>
-    <t>L</t>
+    <t>Lmax</t>
+  </si>
+  <si>
+    <t>Cmax</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%uses inductor value from 24V analysis to calculate Cmax </t>
   </si>
 </sst>
 </file>
@@ -817,7 +778,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -942,11 +903,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -964,6 +956,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -986,6 +981,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1335,26 +1331,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="E1" s="18" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27"/>
+      <c r="E1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20"/>
-      <c r="I1" s="18" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="23"/>
+      <c r="I1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20"/>
-      <c r="M1" s="18" t="s">
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
+      <c r="M1" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="23"/>
     </row>
     <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
@@ -1389,7 +1385,7 @@
       <c r="M2" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="17">
+      <c r="N2" s="20">
         <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
         <v>6.5886173588108662E-5</v>
       </c>
@@ -1397,7 +1393,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1426,15 +1422,15 @@
       <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3">
-        <f>((F19*F14)*(1-F19))/(F26*F23*10^3)</f>
-        <v>8.1111111111111116E-6</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>50</v>
+      <c r="M3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" s="7">
+        <f>((1-(F18))/(8*N2*F25*(F23*10^3)^2))</f>
+        <v>6.6131866766249291E-5</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
@@ -1468,16 +1464,6 @@
       <c r="K4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4">
-        <f>(((1-F18)*B20)/(2*F23*10^3))</f>
-        <v>7.261959422444625E-6</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
@@ -1509,16 +1495,6 @@
       <c r="K5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5">
-        <f>((1-(F18))/(8*N2*F25*(F23*10^3)^2))</f>
-        <v>6.6131866766249291E-5</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="R5" s="11"/>
     </row>
     <row r="6" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
@@ -1551,16 +1527,6 @@
       <c r="K6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" s="7">
-        <f>N2</f>
-        <v>6.5886173588108662E-5</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="7" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E7" s="4" t="s">
@@ -1583,6 +1549,7 @@
       <c r="K7" s="8" t="s">
         <v>30</v>
       </c>
+      <c r="M7" s="13"/>
     </row>
     <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E8" s="4" t="s">
@@ -1608,21 +1575,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="M10" s="13"/>
-    </row>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="E13" s="18" t="s">
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="E13" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -1814,11 +1778,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
       <c r="E24" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F24" s="13">
         <v>0.3</v>
@@ -1827,7 +1791,7 @@
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E25" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F25" s="13">
         <v>0.01</v>
@@ -1836,7 +1800,7 @@
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E26" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F26" s="13">
         <f>F24*F20</f>
@@ -1848,7 +1812,7 @@
     </row>
     <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E27" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F27" s="13">
         <f>F25*F17</f>
@@ -1860,7 +1824,7 @@
     </row>
     <row r="28" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E28" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F28" s="7">
         <f>SQRT(((F20^2)+(3.6^2)))</f>
@@ -1887,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF31E89F-592A-437D-9440-200F7F48CEED}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -1896,31 +1860,32 @@
     <col min="7" max="7" width="4.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="E1" s="18" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="27"/>
+      <c r="E1" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20"/>
-      <c r="I1" s="18" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="23"/>
+      <c r="I1" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20"/>
-      <c r="M1" s="18" t="s">
+      <c r="J1" s="22"/>
+      <c r="K1" s="23"/>
+      <c r="M1" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="N1" s="22"/>
+      <c r="O1" s="23"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1951,17 +1916,17 @@
         <v>7</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="N2">
         <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
-        <v>3.6749321174804939E-6</v>
+        <v>3.6749321174804942E-5</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1990,18 +1955,21 @@
       <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3">
-        <f>((F19*F14)*(1-F19))/(F26*F23*10^3)</f>
-        <v>4.0555555555555553E-7</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="M3" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="18">
+        <f>((1-(F18))/(8*'24V analysis'!N2*F25*(F23*10^3)^2))</f>
+        <v>7.1010161494304677E-5</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2032,18 +2000,8 @@
       <c r="K4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4">
-        <f>(((1-F18)*B20)/(2*F23*10^3))</f>
-        <v>3.8988231889444899E-7</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2073,18 +2031,8 @@
       <c r="K5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="7">
-        <f>'24V analysis'!N6</f>
-        <v>6.5886173588108662E-5</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -2115,7 +2063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
@@ -2136,8 +2084,11 @@
       <c r="K7" s="8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="M7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
@@ -2149,7 +2100,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
@@ -2162,20 +2113,20 @@
       </c>
       <c r="H9" s="12"/>
     </row>
-    <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
+    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="E13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="E13" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -2196,7 +2147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -2215,7 +2166,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
@@ -2358,18 +2309,18 @@
         <v>47</v>
       </c>
       <c r="F23" s="13">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
       <c r="E24" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F24" s="13">
         <v>0.3</v>
@@ -2378,7 +2329,7 @@
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E25" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F25" s="13">
         <v>0.01</v>
@@ -2387,7 +2338,7 @@
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E26" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F26" s="13">
         <f>F24*F20</f>
@@ -2399,7 +2350,7 @@
     </row>
     <row r="27" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E27" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F27" s="14">
         <f>F25*F17</f>

--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6437BE-D93E-4E78-BBBA-A190F34A7002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8FA03E-EF6C-476F-80EE-B5F9B27E1238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="66">
   <si>
     <t>C-rate</t>
   </si>
@@ -728,6 +728,9 @@
   </si>
   <si>
     <t xml:space="preserve">%uses inductor value from 24V analysis to calculate Cmax </t>
+  </si>
+  <si>
+    <t>%chosen to keep rectifier filter cap low</t>
   </si>
 </sst>
 </file>
@@ -1367,7 +1370,7 @@
       </c>
       <c r="F2" s="13">
         <f>F4/SQRT(2)</f>
-        <v>22.941686678496872</v>
+        <v>42.426406871192846</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>7</v>
@@ -1376,8 +1379,8 @@
         <v>26</v>
       </c>
       <c r="J2" s="13">
-        <f>F17/F19</f>
-        <v>32.444444444444443</v>
+        <f>F4</f>
+        <v>60</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>7</v>
@@ -1448,8 +1451,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="13">
-        <f>J2</f>
-        <v>32.444444444444443</v>
+        <v>60</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>7</v>
@@ -1534,7 +1536,7 @@
       </c>
       <c r="F7" s="13">
         <f>SQRT(2/3)*J7</f>
-        <v>17.636326148038883</v>
+        <v>9.5366800652358403</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -1544,7 +1546,7 @@
       </c>
       <c r="J7" s="14">
         <f>F22</f>
-        <v>21.6</v>
+        <v>11.68</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>30</v>
@@ -1603,10 +1605,13 @@
       </c>
       <c r="F14" s="13">
         <f>J2</f>
-        <v>32.444444444444443</v>
+        <v>60</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>7</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
@@ -1707,7 +1712,8 @@
         <v>34</v>
       </c>
       <c r="F19" s="13">
-        <v>0.9</v>
+        <f>F17/J2</f>
+        <v>0.48666666666666664</v>
       </c>
       <c r="G19" s="5"/>
     </row>
@@ -1760,7 +1766,7 @@
       </c>
       <c r="F22" s="13">
         <f>F19*F20</f>
-        <v>21.6</v>
+        <v>11.68</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>30</v>
@@ -1900,7 +1906,7 @@
       </c>
       <c r="F2" s="13">
         <f>F4/SQRT(2)</f>
-        <v>11.470843339248436</v>
+        <v>33.941125496954278</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>7</v>
@@ -1909,8 +1915,8 @@
         <v>26</v>
       </c>
       <c r="J2" s="13">
-        <f>F17/F19</f>
-        <v>16.222222222222221</v>
+        <f>F4</f>
+        <v>48</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>7</v>
@@ -1965,7 +1971,7 @@
       <c r="O3" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="28" t="s">
+      <c r="P3" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1984,8 +1990,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="13">
-        <f>J2</f>
-        <v>16.222222222222221</v>
+        <v>48</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>7</v>
@@ -2069,7 +2074,7 @@
       </c>
       <c r="F7" s="13">
         <f>SQRT(2/3)*J7</f>
-        <v>17.636326148038883</v>
+        <v>5.9604250407723995</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -2079,7 +2084,7 @@
       </c>
       <c r="J7" s="14">
         <f>F22</f>
-        <v>21.6</v>
+        <v>7.2999999999999989</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>30</v>
@@ -2106,7 +2111,7 @@
       </c>
       <c r="F9" s="14">
         <f>SQRT(3)*F2*F7</f>
-        <v>350.4</v>
+        <v>350.39999999999992</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>43</v>
@@ -2141,10 +2146,13 @@
       </c>
       <c r="F14" s="13">
         <f>J2</f>
-        <v>16.222222222222221</v>
+        <v>48</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>7</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
@@ -2245,7 +2253,8 @@
         <v>34</v>
       </c>
       <c r="F19" s="13">
-        <v>0.9</v>
+        <f>F17/J2</f>
+        <v>0.30416666666666664</v>
       </c>
       <c r="G19" s="5"/>
     </row>
@@ -2298,7 +2307,7 @@
       </c>
       <c r="F22" s="13">
         <f>F19*F20</f>
-        <v>21.6</v>
+        <v>7.2999999999999989</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>30</v>

--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8FA03E-EF6C-476F-80EE-B5F9B27E1238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE24CCD-128E-4958-A710-DEE6E1564BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
   <si>
     <t>C-rate</t>
   </si>
@@ -615,22 +615,6 @@
   </si>
   <si>
     <r>
-      <t>ΔV</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>o,max</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>V</t>
     </r>
     <r>
@@ -700,22 +684,6 @@
   </si>
   <si>
     <t>F</t>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L,RMS</t>
-    </r>
   </si>
   <si>
     <t>Lmax</t>
@@ -737,6 +705,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -941,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -984,7 +955,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1319,14 +1295,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB43F6-C991-4FED-A486-EADAA5F16055}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.88671875" customWidth="1"/>
     <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.21875" customWidth="1"/>
@@ -1368,7 +1345,7 @@
       <c r="E2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="28">
         <f>F4/SQRT(2)</f>
         <v>42.426406871192846</v>
       </c>
@@ -1378,7 +1355,7 @@
       <c r="I2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="28">
         <f>F4</f>
         <v>60</v>
       </c>
@@ -1409,7 +1386,7 @@
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="28">
         <v>110</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -1418,7 +1395,7 @@
       <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="28">
         <f>F5</f>
         <v>155.56349186104046</v>
       </c>
@@ -1426,14 +1403,14 @@
         <v>7</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N3" s="7">
         <f>((1-(F18))/(8*N2*F25*(F23*10^3)^2))</f>
         <v>6.6131866766249291E-5</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
@@ -1450,7 +1427,7 @@
       <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="28">
         <v>60</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -1459,7 +1436,7 @@
       <c r="I4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="28">
         <f>B18</f>
         <v>480</v>
       </c>
@@ -1480,7 +1457,7 @@
       <c r="E5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="28">
         <f>SQRT(2)*F3</f>
         <v>155.56349186104046</v>
       </c>
@@ -1490,7 +1467,7 @@
       <c r="I5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="28">
         <f>B19</f>
         <v>700.8</v>
       </c>
@@ -1512,7 +1489,7 @@
       <c r="E6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="28">
         <f>SQRT(2/3)*J6</f>
         <v>2.5193466291910944</v>
       </c>
@@ -1522,7 +1499,7 @@
       <c r="I6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="28">
         <f>F21</f>
         <v>3.0855568633594803</v>
       </c>
@@ -1534,7 +1511,7 @@
       <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="28">
         <f>SQRT(2/3)*J7</f>
         <v>9.5366800652358403</v>
       </c>
@@ -1544,7 +1521,7 @@
       <c r="I7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="29">
         <f>F22</f>
         <v>11.68</v>
       </c>
@@ -1557,7 +1534,7 @@
       <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="28">
         <f>SQRT(3)*F6*F3</f>
         <v>479.99999999999994</v>
       </c>
@@ -1569,7 +1546,7 @@
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="29">
         <f>SQRT(3)*F2*F7</f>
         <v>700.8</v>
       </c>
@@ -1594,7 +1571,7 @@
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="30">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1603,29 +1580,29 @@
       <c r="E14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="32">
         <f>J2</f>
         <v>60</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="28" t="s">
-        <v>65</v>
+      <c r="H14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="28">
         <v>8</v>
       </c>
       <c r="C15" s="5"/>
       <c r="E15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="32">
         <f>J3</f>
         <v>155.56349186104046</v>
       </c>
@@ -1637,7 +1614,7 @@
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="28">
         <f>B5*B15</f>
         <v>20</v>
       </c>
@@ -1647,7 +1624,7 @@
       <c r="E16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="32">
         <f>B16</f>
         <v>20</v>
       </c>
@@ -1659,7 +1636,7 @@
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="28">
         <f>B6*B15</f>
         <v>29.2</v>
       </c>
@@ -1669,7 +1646,7 @@
       <c r="E17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="32">
         <f>B17</f>
         <v>29.2</v>
       </c>
@@ -1681,7 +1658,7 @@
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="28">
         <f>B16*B4</f>
         <v>480</v>
       </c>
@@ -1691,7 +1668,7 @@
       <c r="E18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="32">
         <f>F16/J3</f>
         <v>0.12856486930664501</v>
       </c>
@@ -1701,7 +1678,7 @@
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="28">
         <f>B17*B4</f>
         <v>700.8</v>
       </c>
@@ -1711,7 +1688,7 @@
       <c r="E19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="32">
         <f>F17/J2</f>
         <v>0.48666666666666664</v>
       </c>
@@ -1721,7 +1698,7 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="28">
         <f>B16/B4</f>
         <v>0.83333333333333337</v>
       </c>
@@ -1731,7 +1708,7 @@
       <c r="E20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="32">
         <v>24</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -1742,7 +1719,7 @@
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="29">
         <f>B17/B4</f>
         <v>1.2166666666666666</v>
       </c>
@@ -1752,7 +1729,7 @@
       <c r="E21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="32">
         <f>F18*F20</f>
         <v>3.0855568633594803</v>
       </c>
@@ -1764,7 +1741,7 @@
       <c r="E22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="32">
         <f>F19*F20</f>
         <v>11.68</v>
       </c>
@@ -1776,7 +1753,7 @@
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="32">
         <v>50</v>
       </c>
       <c r="G23" s="5" t="s">
@@ -1790,53 +1767,29 @@
       <c r="E24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="32">
         <v>0.3</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E25" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E26" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="13">
+      <c r="F26" s="29">
         <f>F24*F20</f>
         <v>7.1999999999999993</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="13">
-        <f>F25*F17</f>
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E28" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="7">
-        <f>SQRT(((F20^2)+(3.6^2)))</f>
-        <v>24.268498099388022</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="G26" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1857,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF31E89F-592A-437D-9440-200F7F48CEED}">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -1922,7 +1875,7 @@
         <v>7</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N2">
         <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
@@ -1962,17 +1915,17 @@
         <v>7</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N3" s="18">
         <f>((1-(F18))/(8*'24V analysis'!N2*F25*(F23*10^3)^2))</f>
         <v>7.1010161494304677E-5</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
@@ -2090,7 +2043,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
@@ -2126,7 +2079,7 @@
       <c r="B13" s="26"/>
       <c r="C13" s="27"/>
       <c r="E13" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="22"/>
       <c r="G13" s="23"/>
@@ -2144,15 +2097,15 @@
       <c r="E14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="31">
         <f>J2</f>
         <v>48</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="28" t="s">
-        <v>65</v>
+      <c r="H14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
@@ -2166,7 +2119,7 @@
       <c r="E15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="31">
         <f>J3</f>
         <v>155.56349186104046</v>
       </c>
@@ -2188,7 +2141,7 @@
       <c r="E16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="31">
         <f>B16</f>
         <v>10</v>
       </c>
@@ -2210,7 +2163,7 @@
       <c r="E17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="31">
         <f>B17</f>
         <v>14.6</v>
       </c>
@@ -2232,7 +2185,7 @@
       <c r="E18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="31">
         <f>F16/J3</f>
         <v>6.4282434653322507E-2</v>
       </c>
@@ -2252,7 +2205,7 @@
       <c r="E19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="31">
         <f>F17/J2</f>
         <v>0.30416666666666664</v>
       </c>
@@ -2262,7 +2215,7 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="28">
         <f>B16/B4</f>
         <v>0.41666666666666669</v>
       </c>
@@ -2272,7 +2225,7 @@
       <c r="E20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="31">
         <v>24</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -2283,7 +2236,7 @@
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="29">
         <f>B17/B4</f>
         <v>0.60833333333333328</v>
       </c>
@@ -2293,7 +2246,7 @@
       <c r="E21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="31">
         <f>F18*F20</f>
         <v>1.5427784316797402</v>
       </c>
@@ -2305,7 +2258,7 @@
       <c r="E22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="31">
         <f>F19*F20</f>
         <v>7.2999999999999989</v>
       </c>
@@ -2317,7 +2270,7 @@
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="31">
         <v>50</v>
       </c>
       <c r="G23" s="5" t="s">
@@ -2331,7 +2284,7 @@
       <c r="E24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="31">
         <v>0.3</v>
       </c>
       <c r="G24" s="5"/>
@@ -2340,33 +2293,21 @@
       <c r="E25" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="31">
         <v>0.01</v>
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="E26" s="10" t="s">
+    <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E26" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <f>F24*F20</f>
         <v>7.1999999999999993</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="8" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E27" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="14">
-        <f>F25*F17</f>
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2384,23 +2325,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2589,10 +2513,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2615,20 +2567,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE24CCD-128E-4958-A710-DEE6E1564BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -912,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -934,6 +934,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -955,12 +959,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1311,26 +1309,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
-      <c r="E1" s="21" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="E1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23"/>
-      <c r="I1" s="21" t="s">
+      <c r="F1" s="26"/>
+      <c r="G1" s="27"/>
+      <c r="I1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="22"/>
-      <c r="K1" s="23"/>
-      <c r="M1" s="21" t="s">
+      <c r="J1" s="26"/>
+      <c r="K1" s="27"/>
+      <c r="M1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="22"/>
-      <c r="O1" s="23"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
@@ -1345,7 +1343,7 @@
       <c r="E2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="21">
         <f>F4/SQRT(2)</f>
         <v>42.426406871192846</v>
       </c>
@@ -1355,7 +1353,7 @@
       <c r="I2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="21">
         <f>F4</f>
         <v>60</v>
       </c>
@@ -1386,7 +1384,7 @@
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="21">
         <v>110</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -1395,7 +1393,7 @@
       <c r="I3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="21">
         <f>F5</f>
         <v>155.56349186104046</v>
       </c>
@@ -1427,7 +1425,7 @@
       <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="21">
         <v>60</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -1436,7 +1434,7 @@
       <c r="I4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="21">
         <f>B18</f>
         <v>480</v>
       </c>
@@ -1457,7 +1455,7 @@
       <c r="E5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="21">
         <f>SQRT(2)*F3</f>
         <v>155.56349186104046</v>
       </c>
@@ -1467,7 +1465,7 @@
       <c r="I5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="21">
         <f>B19</f>
         <v>700.8</v>
       </c>
@@ -1489,7 +1487,7 @@
       <c r="E6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="21">
         <f>SQRT(2/3)*J6</f>
         <v>2.5193466291910944</v>
       </c>
@@ -1499,7 +1497,7 @@
       <c r="I6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="21">
         <f>F21</f>
         <v>3.0855568633594803</v>
       </c>
@@ -1511,7 +1509,7 @@
       <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="21">
         <f>SQRT(2/3)*J7</f>
         <v>9.5366800652358403</v>
       </c>
@@ -1521,7 +1519,7 @@
       <c r="I7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="22">
         <f>F22</f>
         <v>11.68</v>
       </c>
@@ -1534,7 +1532,7 @@
       <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="21">
         <f>SQRT(3)*F6*F3</f>
         <v>479.99999999999994</v>
       </c>
@@ -1546,7 +1544,7 @@
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="22">
         <f>SQRT(3)*F2*F7</f>
         <v>700.8</v>
       </c>
@@ -1556,22 +1554,22 @@
     </row>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="E13" s="21" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="E13" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="23">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1580,7 +1578,7 @@
       <c r="E14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="21">
         <f>J2</f>
         <v>60</v>
       </c>
@@ -1595,14 +1593,14 @@
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="21">
         <v>8</v>
       </c>
       <c r="C15" s="5"/>
       <c r="E15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="21">
         <f>J3</f>
         <v>155.56349186104046</v>
       </c>
@@ -1614,7 +1612,7 @@
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="21">
         <f>B5*B15</f>
         <v>20</v>
       </c>
@@ -1624,7 +1622,7 @@
       <c r="E16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="21">
         <f>B16</f>
         <v>20</v>
       </c>
@@ -1636,7 +1634,7 @@
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="21">
         <f>B6*B15</f>
         <v>29.2</v>
       </c>
@@ -1646,7 +1644,7 @@
       <c r="E17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="21">
         <f>B17</f>
         <v>29.2</v>
       </c>
@@ -1658,7 +1656,7 @@
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="21">
         <f>B16*B4</f>
         <v>480</v>
       </c>
@@ -1668,7 +1666,7 @@
       <c r="E18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="21">
         <f>F16/J3</f>
         <v>0.12856486930664501</v>
       </c>
@@ -1678,7 +1676,7 @@
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="21">
         <f>B17*B4</f>
         <v>700.8</v>
       </c>
@@ -1688,7 +1686,7 @@
       <c r="E19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="21">
         <f>F17/J2</f>
         <v>0.48666666666666664</v>
       </c>
@@ -1698,7 +1696,7 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="21">
         <f>B16/B4</f>
         <v>0.83333333333333337</v>
       </c>
@@ -1708,7 +1706,7 @@
       <c r="E20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="21">
         <v>24</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -1719,7 +1717,7 @@
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="22">
         <f>B17/B4</f>
         <v>1.2166666666666666</v>
       </c>
@@ -1729,7 +1727,7 @@
       <c r="E21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="21">
         <f>F18*F20</f>
         <v>3.0855568633594803</v>
       </c>
@@ -1741,7 +1739,7 @@
       <c r="E22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="21">
         <f>F19*F20</f>
         <v>11.68</v>
       </c>
@@ -1753,7 +1751,7 @@
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="21">
         <v>50</v>
       </c>
       <c r="G23" s="5" t="s">
@@ -1761,13 +1759,13 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
       <c r="E24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="21">
         <v>0.3</v>
       </c>
       <c r="G24" s="5"/>
@@ -1776,7 +1774,7 @@
       <c r="E25" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="21">
         <v>0.01</v>
       </c>
       <c r="G25" s="5"/>
@@ -1785,7 +1783,7 @@
       <c r="E26" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="22">
         <f>F24*F20</f>
         <v>7.1999999999999993</v>
       </c>
@@ -1823,26 +1821,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
-      <c r="E1" s="21" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="E1" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23"/>
-      <c r="I1" s="21" t="s">
+      <c r="F1" s="26"/>
+      <c r="G1" s="27"/>
+      <c r="I1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="22"/>
-      <c r="K1" s="23"/>
-      <c r="M1" s="21" t="s">
+      <c r="J1" s="26"/>
+      <c r="K1" s="27"/>
+      <c r="M1" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="22"/>
-      <c r="O1" s="23"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
@@ -2073,16 +2071,16 @@
     </row>
     <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="E13" s="21" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31"/>
+      <c r="E13" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -2097,7 +2095,7 @@
       <c r="E14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="13">
         <f>J2</f>
         <v>48</v>
       </c>
@@ -2119,7 +2117,7 @@
       <c r="E15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="13">
         <f>J3</f>
         <v>155.56349186104046</v>
       </c>
@@ -2141,7 +2139,7 @@
       <c r="E16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="13">
         <f>B16</f>
         <v>10</v>
       </c>
@@ -2163,7 +2161,7 @@
       <c r="E17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="13">
         <f>B17</f>
         <v>14.6</v>
       </c>
@@ -2185,7 +2183,7 @@
       <c r="E18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="13">
         <f>F16/J3</f>
         <v>6.4282434653322507E-2</v>
       </c>
@@ -2205,7 +2203,7 @@
       <c r="E19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="13">
         <f>F17/J2</f>
         <v>0.30416666666666664</v>
       </c>
@@ -2215,7 +2213,7 @@
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="21">
         <f>B16/B4</f>
         <v>0.41666666666666669</v>
       </c>
@@ -2225,7 +2223,7 @@
       <c r="E20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="13">
         <v>24</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -2236,7 +2234,7 @@
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="22">
         <f>B17/B4</f>
         <v>0.60833333333333328</v>
       </c>
@@ -2246,7 +2244,7 @@
       <c r="E21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="13">
         <f>F18*F20</f>
         <v>1.5427784316797402</v>
       </c>
@@ -2258,7 +2256,7 @@
       <c r="E22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="13">
         <f>F19*F20</f>
         <v>7.2999999999999989</v>
       </c>
@@ -2270,7 +2268,7 @@
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="13">
         <v>50</v>
       </c>
       <c r="G23" s="5" t="s">
@@ -2278,13 +2276,13 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
       <c r="E24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="13">
         <v>0.3</v>
       </c>
       <c r="G24" s="5"/>
@@ -2293,13 +2291,13 @@
       <c r="E25" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="13">
         <v>0.01</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E26" s="33" t="s">
+      <c r="E26" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F26" s="14">
@@ -2325,6 +2323,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2513,38 +2528,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2567,9 +2554,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE24CCD-128E-4958-A710-DEE6E1564BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -2323,23 +2323,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2528,10 +2511,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2554,20 +2565,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE24CCD-128E-4958-A710-DEE6E1564BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD8F7CB-AF91-4034-9EF8-A66BC5E94E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="68">
   <si>
     <t>C-rate</t>
   </si>
@@ -699,6 +699,70 @@
   </si>
   <si>
     <t>%chosen to keep rectifier filter cap low</t>
+  </si>
+  <si>
+    <r>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>term,max</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>term,min</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VOC</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>min</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>VOC</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>max</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -912,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -959,6 +1023,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1444,7 +1511,7 @@
     </row>
     <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B5">
         <v>2.5</v>
@@ -1476,7 +1543,7 @@
     </row>
     <row r="6" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="B6" s="7">
         <v>3.65</v>
@@ -1506,6 +1573,15 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="33">
+        <v>3.1</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>7</v>
+      </c>
       <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
@@ -1529,6 +1605,15 @@
       <c r="M7" s="13"/>
     </row>
     <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A8" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="33">
+        <v>3.45</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>7</v>
+      </c>
       <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
@@ -1697,8 +1782,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="21">
-        <f>B16/B4</f>
-        <v>0.83333333333333337</v>
+        <v>7.6E-3</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>15</v>
@@ -1718,8 +1802,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="22">
-        <f>B17/B4</f>
-        <v>1.2166666666666666</v>
+        <v>1.2E-2</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>15</v>
@@ -2323,6 +2406,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2511,38 +2611,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2565,9 +2637,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD8F7CB-AF91-4034-9EF8-A66BC5E94E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F6444C-A616-496B-93D5-209210E97215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="68">
   <si>
     <t>C-rate</t>
   </si>
@@ -976,7 +976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1023,9 +1023,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1361,21 +1360,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB43F6-C991-4FED-A486-EADAA5F16055}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>17</v>
       </c>
@@ -1397,12 +1396,12 @@
       <c r="N1" s="26"/>
       <c r="O1" s="27"/>
     </row>
-    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>3</v>
+      <c r="B2" s="32">
+        <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>2</v>
@@ -1432,17 +1431,17 @@
       </c>
       <c r="N2" s="20">
         <f>((F17*(1-(F17/F15)))/(F26*F23*10^3))</f>
-        <v>6.5886173588108662E-5</v>
+        <v>1.9765852076432595E-4</v>
       </c>
       <c r="O2" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="32">
         <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1472,19 +1471,19 @@
       </c>
       <c r="N3" s="7">
         <f>((1-(F18))/(8*N2*F25*(F23*10^3)^2))</f>
-        <v>6.6131866766249291E-5</v>
+        <v>2.1929478272464733E-5</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="32">
         <f>B2*B3</f>
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -1503,18 +1502,18 @@
       </c>
       <c r="J4" s="21">
         <f>B18</f>
-        <v>480</v>
+        <v>165.63200000000001</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B5">
-        <v>2.5</v>
+      <c r="B5" s="32">
+        <v>2.5880000000000001</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>7</v>
@@ -1534,21 +1533,21 @@
       </c>
       <c r="J5" s="21">
         <f>B19</f>
-        <v>700.8</v>
+        <v>233.6</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="R5" s="11"/>
     </row>
-    <row r="6" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="32">
         <v>3.65</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1556,7 +1555,7 @@
       </c>
       <c r="F6" s="21">
         <f>SQRT(2/3)*J6</f>
-        <v>2.5193466291910944</v>
+        <v>0.86934254351287354</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>30</v>
@@ -1566,20 +1565,20 @@
       </c>
       <c r="J6" s="21">
         <f>F21</f>
-        <v>3.0855568633594803</v>
+        <v>1.0647228216499112</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="32" t="s">
+    <row r="7" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="33">
-        <v>3.1</v>
-      </c>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -1587,7 +1586,7 @@
       </c>
       <c r="F7" s="21">
         <f>SQRT(2/3)*J7</f>
-        <v>9.5366800652358403</v>
+        <v>3.1788933550786131</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -1597,21 +1596,21 @@
       </c>
       <c r="J7" s="22">
         <f>F22</f>
-        <v>11.68</v>
+        <v>3.8933333333333331</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>30</v>
       </c>
       <c r="M7" s="13"/>
     </row>
-    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A8" s="32" t="s">
+    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="33">
-        <v>3.45</v>
-      </c>
-      <c r="C8" s="34" t="s">
+      <c r="B8" s="32">
+        <v>3.5579999999999998</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -1619,26 +1618,46 @@
       </c>
       <c r="F8" s="21">
         <f>SQRT(3)*F6*F3</f>
-        <v>479.99999999999994</v>
+        <v>165.63199999999998</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="33">
+        <v>7.6E-3</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="22">
         <f>SQRT(3)*F2*F7</f>
-        <v>700.8</v>
+        <v>233.59999999999997</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="22">
+        <v>1.14E-2</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>18</v>
       </c>
@@ -1650,7 +1669,7 @@
       <c r="F13" s="26"/>
       <c r="G13" s="27"/>
     </row>
-    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -1674,7 +1693,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -1693,13 +1712,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B16" s="21">
         <f>B5*B15</f>
-        <v>20</v>
+        <v>20.704000000000001</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
@@ -1709,15 +1728,15 @@
       </c>
       <c r="F16" s="21">
         <f>B16</f>
-        <v>20</v>
+        <v>20.704000000000001</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="B17" s="21">
         <f>B6*B15</f>
@@ -1737,13 +1756,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="21">
         <f>B16*B4</f>
-        <v>480</v>
+        <v>165.63200000000001</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
@@ -1753,17 +1772,17 @@
       </c>
       <c r="F18" s="21">
         <f>F16/J3</f>
-        <v>0.12856486930664501</v>
+        <v>0.1330903527062389</v>
       </c>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="21">
         <f>B17*B4</f>
-        <v>700.8</v>
+        <v>233.6</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>16</v>
@@ -1777,12 +1796,13 @@
       </c>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="21">
-        <v>7.6E-3</v>
+        <f>B15*B9</f>
+        <v>6.08E-2</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>15</v>
@@ -1791,18 +1811,20 @@
         <v>29</v>
       </c>
       <c r="F20" s="21">
-        <v>24</v>
+        <f>B4</f>
+        <v>8</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="22">
-        <v>1.2E-2</v>
+        <f>B15*B10</f>
+        <v>9.1200000000000003E-2</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>15</v>
@@ -1812,25 +1834,25 @@
       </c>
       <c r="F21" s="21">
         <f>F18*F20</f>
-        <v>3.0855568633594803</v>
+        <v>1.0647228216499112</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="E22" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="21">
         <f>F19*F20</f>
-        <v>11.68</v>
+        <v>3.8933333333333331</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
@@ -1841,7 +1863,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="28"/>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -1853,7 +1875,7 @@
       </c>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="E25" s="10" t="s">
         <v>54</v>
       </c>
@@ -1862,13 +1884,13 @@
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E26" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F26" s="22">
         <f>F24*F20</f>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>30</v>
@@ -1892,18 +1914,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF31E89F-592A-437D-9440-200F7F48CEED}">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.88671875" customWidth="1"/>
+    <col min="16" max="16" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>17</v>
       </c>
@@ -1925,7 +1947,7 @@
       <c r="N1" s="26"/>
       <c r="O1" s="27"/>
     </row>
-    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1966,7 +1988,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2000,7 +2022,7 @@
       </c>
       <c r="N3" s="18">
         <f>((1-(F18))/(8*'24V analysis'!N2*F25*(F23*10^3)^2))</f>
-        <v>7.1010161494304677E-5</v>
+        <v>2.3670053831434897E-5</v>
       </c>
       <c r="O3" s="19" t="s">
         <v>58</v>
@@ -2009,7 +2031,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2040,7 +2062,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2071,7 +2093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -2102,7 +2124,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
@@ -2127,7 +2149,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
@@ -2139,7 +2161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E9" s="6" t="s">
         <v>12</v>
       </c>
@@ -2152,8 +2174,8 @@
       </c>
       <c r="H9" s="12"/>
     </row>
-    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>19</v>
       </c>
@@ -2165,7 +2187,7 @@
       <c r="F13" s="26"/>
       <c r="G13" s="27"/>
     </row>
-    <row r="14" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -2189,7 +2211,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>10</v>
       </c>
@@ -2208,7 +2230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
@@ -2230,7 +2252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -2252,7 +2274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
@@ -2272,7 +2294,7 @@
       </c>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
@@ -2292,7 +2314,7 @@
       </c>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
@@ -2313,7 +2335,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
@@ -2335,7 +2357,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="E22" s="4" t="s">
         <v>38</v>
       </c>
@@ -2347,7 +2369,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
@@ -2358,7 +2380,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="28"/>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -2370,7 +2392,7 @@
       </c>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="E25" s="4" t="s">
         <v>51</v>
       </c>
@@ -2379,7 +2401,7 @@
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E26" s="24" t="s">
         <v>53</v>
       </c>

--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCB0E35-FE9A-47E8-B90C-354B871354DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407A611E-602D-435A-9654-29D23899B8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
         <v>184.83199999999994</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
@@ -1566,7 +1566,7 @@
         <v>220.79999999999998</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -2361,23 +2361,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2566,10 +2549,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2592,20 +2603,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -2361,6 +2361,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2549,38 +2566,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2603,9 +2592,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407A611E-602D-435A-9654-29D23899B8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95191D12-792F-4EE7-A98D-F650933CA0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F2" s="20">
         <f>F4/SQRT(2)</f>
-        <v>42.426406871192846</v>
+        <v>24.041630560342615</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J2" s="20">
         <f>F4</f>
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>7</v>
@@ -1425,7 +1425,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="20">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F7" s="20">
         <f>SQRT(2/3)*J7</f>
-        <v>3.0047074178140321</v>
+        <v>5.3024248549659383</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>28</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J7" s="21">
         <f>F22</f>
-        <v>3.68</v>
+        <v>6.4941176470588236</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>28</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="F14" s="20">
         <f>J2</f>
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>7</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F19" s="20">
         <f>F17/J2</f>
-        <v>0.46</v>
+        <v>0.81176470588235294</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F22" s="20">
         <f>F19*F20</f>
-        <v>3.68</v>
+        <v>6.4941176470588236</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>28</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F2" s="12">
         <f>F4/SQRT(2)</f>
-        <v>33.941125496954278</v>
+        <v>19.091883092036781</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="J2" s="12">
         <f>F4</f>
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>7</v>
@@ -1960,7 +1960,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="12">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F7" s="12">
         <f>SQRT(2/3)*J7</f>
-        <v>1.87794213613377</v>
+        <v>3.3385637975711471</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>28</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="J7" s="13">
         <f>F22</f>
-        <v>2.3000000000000003</v>
+        <v>4.0888888888888895</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>28</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F9" s="13">
         <f>SQRT(3)*F2*F7</f>
-        <v>110.4</v>
+        <v>110.39999999999999</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>41</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F14" s="12">
         <f>J2</f>
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>7</v>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F19" s="12">
         <f>F17/J2</f>
-        <v>0.28750000000000003</v>
+        <v>0.51111111111111118</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F22" s="12">
         <f>F19*F20</f>
-        <v>2.3000000000000003</v>
+        <v>4.0888888888888895</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>28</v>
@@ -2361,23 +2361,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2566,10 +2549,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2592,20 +2603,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95191D12-792F-4EE7-A98D-F650933CA0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3832F5-9FE4-4E90-A7DB-09BABA0F1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F2" s="20">
         <f>F4/SQRT(2)</f>
-        <v>24.041630560342615</v>
+        <v>26.51650429449553</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J2" s="20">
         <f>F4</f>
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>7</v>
@@ -1425,7 +1425,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="20">
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="F7" s="20">
         <f>SQRT(2/3)*J7</f>
-        <v>5.3024248549659383</v>
+        <v>4.8075318685024504</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>28</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J7" s="21">
         <f>F22</f>
-        <v>6.4941176470588236</v>
+        <v>5.8879999999999999</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>28</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="F9" s="21">
         <f>SQRT(3)*F2*F7</f>
-        <v>220.79999999999998</v>
+        <v>220.79999999999993</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>41</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="F14" s="20">
         <f>J2</f>
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>7</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F19" s="20">
         <f>F17/J2</f>
-        <v>0.81176470588235294</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F22" s="20">
         <f>F19*F20</f>
-        <v>6.4941176470588236</v>
+        <v>5.8879999999999999</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>28</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F2" s="12">
         <f>F4/SQRT(2)</f>
-        <v>19.091883092036781</v>
+        <v>20.85965004500315</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="J2" s="12">
         <f>F4</f>
-        <v>27</v>
+        <v>29.5</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>7</v>
@@ -1960,7 +1960,7 @@
         <v>18</v>
       </c>
       <c r="F4" s="12">
-        <v>27</v>
+        <v>29.5</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F7" s="12">
         <f>SQRT(2/3)*J7</f>
-        <v>3.3385637975711471</v>
+        <v>3.0556346621837611</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>28</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="J7" s="13">
         <f>F22</f>
-        <v>4.0888888888888895</v>
+        <v>3.7423728813559323</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>28</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F9" s="13">
         <f>SQRT(3)*F2*F7</f>
-        <v>110.39999999999999</v>
+        <v>110.39999999999998</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>41</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F14" s="12">
         <f>J2</f>
-        <v>27</v>
+        <v>29.5</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>7</v>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F19" s="12">
         <f>F17/J2</f>
-        <v>0.51111111111111118</v>
+        <v>0.46779661016949153</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F22" s="12">
         <f>F19*F20</f>
-        <v>4.0888888888888895</v>
+        <v>3.7423728813559323</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>28</v>

--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3832F5-9FE4-4E90-A7DB-09BABA0F1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D73822-DF48-4CA8-877B-7951E675B3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
@@ -2361,6 +2361,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2549,38 +2566,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2603,9 +2592,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D73822-DF48-4CA8-877B-7951E675B3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E616171-4025-49A1-8B30-8BE135AC8890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
     <sheet name="12V analysis" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="68">
   <si>
     <t>C-rate</t>
   </si>
@@ -699,6 +699,18 @@
       </rPr>
       <t>term,min</t>
     </r>
+  </si>
+  <si>
+    <t>Max 2A range Is</t>
+  </si>
+  <si>
+    <t>1.46A</t>
+  </si>
+  <si>
+    <t>Max 8A  range Is</t>
+  </si>
+  <si>
+    <t>3.68A</t>
   </si>
 </sst>
 </file>
@@ -1303,6 +1315,7 @@
     <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.33203125" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
@@ -1647,7 +1660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>62</v>
       </c>
@@ -1669,7 +1682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
@@ -1689,7 +1702,7 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
@@ -1709,7 +1722,7 @@
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
@@ -1730,8 +1743,14 @@
       <c r="G20" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M20" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>12</v>
       </c>
@@ -1752,8 +1771,14 @@
       <c r="G21" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="M21" t="s">
+        <v>66</v>
+      </c>
+      <c r="N21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E22" s="3" t="s">
         <v>36</v>
       </c>
@@ -1765,7 +1790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E23" s="3" t="s">
         <v>45</v>
       </c>
@@ -1776,7 +1801,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
       <c r="C24" s="27"/>
@@ -1788,7 +1813,7 @@
       </c>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E25" s="9" t="s">
         <v>52</v>
       </c>
@@ -1797,7 +1822,7 @@
       </c>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E26" s="5" t="s">
         <v>53</v>
       </c>
@@ -2361,23 +2386,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2566,10 +2574,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2592,20 +2628,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D73822-DF48-4CA8-877B-7951E675B3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E616171-4025-49A1-8B30-8BE135AC8890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
     <sheet name="12V analysis" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="68">
   <si>
     <t>C-rate</t>
   </si>
@@ -699,6 +699,18 @@
       </rPr>
       <t>term,min</t>
     </r>
+  </si>
+  <si>
+    <t>Max 2A range Is</t>
+  </si>
+  <si>
+    <t>1.46A</t>
+  </si>
+  <si>
+    <t>Max 8A  range Is</t>
+  </si>
+  <si>
+    <t>3.68A</t>
   </si>
 </sst>
 </file>
@@ -1303,6 +1315,7 @@
     <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.33203125" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
@@ -1647,7 +1660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>62</v>
       </c>
@@ -1669,7 +1682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
@@ -1689,7 +1702,7 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
@@ -1709,7 +1722,7 @@
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
@@ -1730,8 +1743,14 @@
       <c r="G20" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M20" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>12</v>
       </c>
@@ -1752,8 +1771,14 @@
       <c r="G21" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="M21" t="s">
+        <v>66</v>
+      </c>
+      <c r="N21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E22" s="3" t="s">
         <v>36</v>
       </c>
@@ -1765,7 +1790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E23" s="3" t="s">
         <v>45</v>
       </c>
@@ -1776,7 +1801,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
       <c r="C24" s="27"/>
@@ -1788,7 +1813,7 @@
       </c>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.35">
       <c r="E25" s="9" t="s">
         <v>52</v>
       </c>
@@ -1797,7 +1822,7 @@
       </c>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E26" s="5" t="s">
         <v>53</v>
       </c>

--- a/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
+++ b/Battery Charger Project/Excel/Calculations/Component calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verrazano\Acedemic\Research\Battery-Charger\Battery Charger Project\Excel\Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E616171-4025-49A1-8B30-8BE135AC8890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5297D8D-99FC-44D4-9AEC-A30684E1A046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8EA801AC-1218-4C2A-8BFC-BC5B39F04A2A}"/>
   </bookViews>
   <sheets>
     <sheet name="24V analysis" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="69">
   <si>
     <t>C-rate</t>
   </si>
@@ -711,6 +711,9 @@
   </si>
   <si>
     <t>3.68A</t>
+  </si>
+  <si>
+    <t>Max current after ripple in 8A range</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB43F6-C991-4FED-A486-EADAA5F16055}">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
@@ -1315,12 +1318,12 @@
     <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="2.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>15</v>
       </c>
@@ -1341,8 +1344,17 @@
       </c>
       <c r="N1" s="25"/>
       <c r="O1" s="26"/>
-    </row>
-    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="Q1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="S1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1383,7 +1395,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1423,7 +1435,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1454,7 +1466,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>63</v>
       </c>
@@ -1486,7 +1498,7 @@
       </c>
       <c r="R5" s="10"/>
     </row>
-    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1517,7 +1529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -1549,7 +1561,7 @@
       </c>
       <c r="M7" s="12"/>
     </row>
-    <row r="8" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1570,7 +1582,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="16.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E9" s="5" t="s">
         <v>10</v>
       </c>
@@ -1582,8 +1594,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="28" t="s">
         <v>16</v>
       </c>
@@ -1595,7 +1607,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -1619,7 +1631,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1638,7 +1650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>63</v>
       </c>
@@ -2386,23 +2398,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009660838691862E40BA8A9FCF4672D404" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57f0f8c66996a8cfd8079b5f5cbc1044">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="77b6129a-f613-4ff9-b238-21504ab3c311" xmlns:ns4="e5775723-78a2-49b3-980c-6ad0b4b03e58" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97be24bc9c367c471a14e5d43da4af43" ns3:_="" ns4:_="">
     <xsd:import namespace="77b6129a-f613-4ff9-b238-21504ab3c311"/>
@@ -2591,10 +2586,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="77b6129a-f613-4ff9-b238-21504ab3c311" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
+    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2617,20 +2640,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F510E196-854A-4018-94EA-77433BC9C36C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69E919-C42D-4F67-B937-7A9547F9358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77b6129a-f613-4ff9-b238-21504ab3c311"/>
-    <ds:schemaRef ds:uri="e5775723-78a2-49b3-980c-6ad0b4b03e58"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>